--- a/output/pdf_financials_xlsx/AGH.H.xlsx
+++ b/output/pdf_financials_xlsx/AGH.H.xlsx
@@ -1219,40 +1219,40 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.083826</v>
+        <v>-0.083826</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.408291</v>
+        <v>-0.408291</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.429783</v>
+        <v>-0.429783</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.367241</v>
+        <v>-0.367241</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.285978</v>
+        <v>-0.285978</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.085661</v>
+        <v>-0.085661</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.130785</v>
+        <v>-0.130785</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.185375</v>
+        <v>-0.185375</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.291156</v>
+        <v>-0.291156</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.196842</v>
+        <v>-0.196842</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.180274</v>
+        <v>-0.180274</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.158475</v>
+        <v>-0.158475</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>-0.18391</v>
@@ -1503,40 +1503,40 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.083826</v>
+        <v>-0.083826</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.408291</v>
+        <v>-0.408291</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.429783</v>
+        <v>-0.429783</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.367241</v>
+        <v>-0.367241</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.285978</v>
+        <v>-0.285978</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.085661</v>
+        <v>-0.085661</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.130785</v>
+        <v>-0.130785</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.185375</v>
+        <v>-0.185375</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.291156</v>
+        <v>-0.291156</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.196842</v>
+        <v>-0.196842</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.180274</v>
+        <v>-0.180274</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>0.158475</v>
+        <v>-0.158475</v>
       </c>
       <c r="N20" s="3" t="n">
         <v>-0.18391</v>
@@ -1668,40 +1668,40 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.083826</v>
+        <v>-0.083826</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.408291</v>
+        <v>-0.408291</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.429783</v>
+        <v>-0.429783</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.367241</v>
+        <v>-0.367241</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.285978</v>
+        <v>-0.285978</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.085661</v>
+        <v>-0.085661</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.130785</v>
+        <v>-0.130785</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.185375</v>
+        <v>-0.185375</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.291156</v>
+        <v>-0.291156</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.196842</v>
+        <v>-0.196842</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.180274</v>
+        <v>-0.180274</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>0.158475</v>
+        <v>-0.158475</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>-0.18391</v>
@@ -1966,40 +1966,40 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.083826</v>
+        <v>-0.083826</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.408291</v>
+        <v>-0.408291</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.429783</v>
+        <v>-0.429783</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.367241</v>
+        <v>-0.367241</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.285978</v>
+        <v>-0.285978</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.085661</v>
+        <v>-0.085661</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.130785</v>
+        <v>-0.130785</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.185375</v>
+        <v>-0.185375</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.291156</v>
+        <v>-0.291156</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.196842</v>
+        <v>-0.196842</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.180274</v>
+        <v>-0.180274</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>0.158475</v>
+        <v>-0.158475</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>-0.18391</v>
@@ -2076,40 +2076,40 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.083826</v>
+        <v>-0.083826</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.408291</v>
+        <v>-0.408291</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.429783</v>
+        <v>-0.429783</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.367241</v>
+        <v>-0.367241</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.285978</v>
+        <v>-0.285978</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.085661</v>
+        <v>-0.085661</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.130785</v>
+        <v>-0.130785</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.185375</v>
+        <v>-0.185375</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.291156</v>
+        <v>-0.291156</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.196842</v>
+        <v>-0.196842</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.180274</v>
+        <v>-0.180274</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.158475</v>
+        <v>-0.158475</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>-0.18391</v>
@@ -2218,40 +2218,40 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>-0</v>
@@ -5682,49 +5682,49 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.557511</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.546821</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.46029</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.46271</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.433605</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.026</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.026</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.034817</v>
       </c>
       <c r="K92" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.046206</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.0249</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>0.03015</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>0.01375</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>0.01375</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>0.041451</v>
       </c>
     </row>
     <row r="93">
@@ -6040,13 +6040,13 @@
         <v>-0.185374</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>0.291156</v>
+        <v>-0.291156</v>
       </c>
       <c r="K99" s="3" t="n">
-        <v>0.196842</v>
+        <v>-0.196842</v>
       </c>
       <c r="L99" s="3" t="n">
-        <v>0.180274</v>
+        <v>-0.180274</v>
       </c>
       <c r="M99" s="3" t="n">
         <v>-0.158475</v>
@@ -7061,31 +7061,31 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>-0.051002</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-0.009575</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-0.558465</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-0.049131</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-0.02239</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-0.007915999999999999</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-0.004387</v>
       </c>
       <c r="I118" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-0.007353</v>
       </c>
       <c r="K118" s="3" t="n">
         <v>0</v>
@@ -7094,16 +7094,16 @@
         <v>0</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>-0.236127</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>-0.007944</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0</v>
+        <v>-0.044477</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0</v>
+        <v>0.013775</v>
       </c>
       <c r="Q118" s="3" t="n">
         <v>0</v>
@@ -9248,7 +9248,11 @@
           <t>Reserves (note 9)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -12822,7 +12826,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
@@ -13792,7 +13800,11 @@
           <t>Reserves (notes 9 and 10)</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -15786,7 +15798,11 @@
           <t>Impairment of exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>-</t>
@@ -15976,7 +15992,11 @@
           <t>Disposal to interest in exploration and evaluation expenditures (note 7)</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
@@ -17124,7 +17144,11 @@
           <t>Additions to interest in exploration and evaluation expenditures (note 7)</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>-</t>
@@ -19890,7 +19914,11 @@
           <t>Additions to interest in exploration property and exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E128" s="5" t="n">
         <v>-0.051002</v>
       </c>
@@ -22898,7 +22926,11 @@
           <t>Change in accrued exploration and evaluation expenditures $</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
@@ -25190,7 +25222,11 @@
           <t>Change in accrued exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E184" t="inlineStr">
         <is>
           <t>-</t>
@@ -29549,10 +29585,10 @@
         </is>
       </c>
       <c r="L230" s="5" t="n">
-        <v>0.185375</v>
+        <v>-0.185375</v>
       </c>
       <c r="M230" s="5" t="n">
-        <v>0.291156</v>
+        <v>-0.291156</v>
       </c>
       <c r="N230" t="inlineStr">
         <is>
@@ -29560,13 +29596,13 @@
         </is>
       </c>
       <c r="O230" s="5" t="n">
-        <v>0.180274</v>
+        <v>-0.180274</v>
       </c>
       <c r="P230" s="5" t="n">
-        <v>0.158475</v>
+        <v>-0.158475</v>
       </c>
       <c r="Q230" s="5" t="n">
-        <v>0.18391</v>
+        <v>-0.18391</v>
       </c>
       <c r="R230" t="inlineStr">
         <is>
@@ -30112,10 +30148,10 @@
         </is>
       </c>
       <c r="M236" s="5" t="n">
-        <v>0.291156</v>
+        <v>-0.291156</v>
       </c>
       <c r="N236" s="5" t="n">
-        <v>0.196842</v>
+        <v>-0.196842</v>
       </c>
       <c r="O236" t="inlineStr">
         <is>
@@ -30802,28 +30838,28 @@
         </is>
       </c>
       <c r="E244" s="5" t="n">
-        <v>0.083826</v>
+        <v>-0.083826</v>
       </c>
       <c r="F244" s="5" t="n">
-        <v>0.408291</v>
+        <v>-0.408291</v>
       </c>
       <c r="G244" s="5" t="n">
-        <v>0.429783</v>
+        <v>-0.429783</v>
       </c>
       <c r="H244" s="5" t="n">
-        <v>0.367241</v>
+        <v>-0.367241</v>
       </c>
       <c r="I244" s="5" t="n">
-        <v>0.285978</v>
+        <v>-0.285978</v>
       </c>
       <c r="J244" s="5" t="n">
-        <v>0.085661</v>
+        <v>-0.085661</v>
       </c>
       <c r="K244" s="5" t="n">
-        <v>0.130785</v>
+        <v>-0.130785</v>
       </c>
       <c r="L244" s="5" t="n">
-        <v>0.185374</v>
+        <v>-0.185374</v>
       </c>
       <c r="M244" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/AGH.H.xlsx
+++ b/output/pdf_financials_xlsx/AGH.H.xlsx
@@ -925,16 +925,16 @@
         <v>0.06</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.080054</v>
+        <v>0.18391</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.06</v>
+        <v>0.168509</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.06</v>
+        <v>0.137076</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.08</v>
+        <v>0.210986</v>
       </c>
     </row>
     <row r="11">
@@ -980,16 +980,16 @@
         <v>-0.06</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-0.080054</v>
+        <v>-0.18391</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-0.06</v>
+        <v>-0.168509</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-0.06</v>
+        <v>-0.137076</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>-0.08</v>
+        <v>-0.210986</v>
       </c>
     </row>
     <row r="12">
@@ -1002,49 +1002,49 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.006476</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.010359</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.004388</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002032</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-8.000000000000001e-05</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-3.5e-05</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-2.5e-05</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-2.5e-05</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001345</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001014</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000692</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000385</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-9.000000000000001e-05</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-8.8e-05</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000113</v>
       </c>
     </row>
     <row r="13">
@@ -1969,49 +1969,49 @@
         <v>-0.083826</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.408291</v>
+        <v>-0.401815</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.429783</v>
+        <v>-0.419424</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.367241</v>
+        <v>-0.362853</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.285978</v>
+        <v>-0.283946</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.085661</v>
+        <v>-0.085581</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.130785</v>
+        <v>-0.13075</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.185375</v>
+        <v>-0.18535</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.291156</v>
+        <v>-0.291131</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.196842</v>
+        <v>-0.195497</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.180274</v>
+        <v>-0.17926</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.158475</v>
+        <v>-0.157783</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.18391</v>
+        <v>-0.183525</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>0.05154</v>
+        <v>0.05163</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.097689</v>
+        <v>-0.09760099999999999</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>0.582284</v>
+        <v>0.5823970000000001</v>
       </c>
     </row>
     <row r="28">
@@ -2079,49 +2079,49 @@
         <v>-0.083826</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.408291</v>
+        <v>-0.401815</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.429783</v>
+        <v>-0.419424</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.367241</v>
+        <v>-0.362853</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.285978</v>
+        <v>-0.283946</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.085661</v>
+        <v>-0.085581</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.130785</v>
+        <v>-0.13075</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.185375</v>
+        <v>-0.18535</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.291156</v>
+        <v>-0.291131</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.196842</v>
+        <v>-0.195497</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.180274</v>
+        <v>-0.17926</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.158475</v>
+        <v>-0.157783</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.18391</v>
+        <v>-0.183525</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>0.05154</v>
+        <v>0.05163</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.097689</v>
+        <v>-0.09760099999999999</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>0.582284</v>
+        <v>0.5823970000000001</v>
       </c>
     </row>
     <row r="30">
@@ -2382,37 +2382,37 @@
         <v>0.144572</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.040042</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.00583</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.205812</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.29727</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.228456</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.217171</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.051153</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.024531</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.02915</v>
       </c>
     </row>
     <row r="35">
@@ -2492,37 +2492,37 @@
         <v>0.144572</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.040042</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.00583</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.205812</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.29727</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.228456</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.217171</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.051153</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.413333</v>
+        <v>0.437864</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>0.362525</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.914198</v>
+        <v>0.943348</v>
       </c>
     </row>
     <row r="37">
@@ -3152,37 +3152,37 @@
         <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.040042</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.00583</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.205812</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.29727</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0.327685</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.233456</v>
+        <v>0.005</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.22302</v>
+        <v>0.005849</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.061537</v>
+        <v>0.010384</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.028381</v>
+        <v>0.00385</v>
       </c>
       <c r="P48" s="3" t="n">
         <v>0.004937</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.035186</v>
+        <v>0.006036</v>
       </c>
     </row>
     <row r="49">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -9808,7 +9808,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -25986,7 +25986,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -26080,7 +26080,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -29370,7 +29370,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -30006,7 +30006,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">

--- a/output/pdf_financials_xlsx/AGH.H.xlsx
+++ b/output/pdf_financials_xlsx/AGH.H.xlsx
@@ -6694,7 +6694,7 @@
         <v>0</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001868</v>
       </c>
       <c r="I111" s="3" t="n">
         <v>0</v>
@@ -6938,10 +6938,10 @@
         <v>0</v>
       </c>
       <c r="P115" s="3" t="n">
-        <v>0</v>
+        <v>0.09024500000000001</v>
       </c>
       <c r="Q115" s="3" t="n">
-        <v>0</v>
+        <v>0.241597</v>
       </c>
     </row>
     <row r="116">
@@ -7232,13 +7232,13 @@
         <v>0</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>0</v>
+        <v>-0.00655</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>0</v>
+        <v>-0.010415</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>0</v>
+        <v>-0.001125</v>
       </c>
       <c r="G121" s="3" t="n">
         <v>0</v>
@@ -7991,7 +7991,7 @@
         <v>0</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001868</v>
       </c>
       <c r="I134" s="3" t="n">
         <v>0</v>
@@ -8046,7 +8046,7 @@
         <v>-0.101614</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>-0.032957</v>
+        <v>-0.034825</v>
       </c>
       <c r="I135" s="3" t="n">
         <v>-0.141984</v>
@@ -15162,7 +15162,11 @@
           <t>Proceeds from sale of marketable securities (note 15)</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -16188,7 +16192,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -20574,7 +20582,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
           <t>-</t>
@@ -21246,7 +21258,11 @@
           <t>Share repurchase (note 8(b))</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
           <t>-</t>
@@ -22276,7 +22292,11 @@
           <t>Share repurchase (note 8(b)(1))</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>
@@ -24342,7 +24362,11 @@
           <t>Share repurchase</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
           <t>-</t>
